--- a/data/trans_orig/P36B13-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B13-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42258</t>
+          <t>40419</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>23539</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44060</t>
+          <t>44133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48563</t>
+          <t>46836</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77903</t>
+          <t>76831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76724</t>
+          <t>75979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111125</t>
+          <t>111097</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75192</t>
+          <t>76334</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108465</t>
+          <t>108099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160089</t>
+          <t>159028</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>204612</t>
+          <t>206836</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>165313</t>
+          <t>167702</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>206512</t>
+          <t>208417</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>169938</t>
+          <t>169768</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>210483</t>
+          <t>208691</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>347496</t>
+          <t>344752</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>404823</t>
+          <t>404846</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83194</t>
+          <t>80861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117019</t>
+          <t>115809</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58496</t>
+          <t>58116</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89978</t>
+          <t>88816</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>151089</t>
+          <t>152457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>197925</t>
+          <t>199476</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>21116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14244</t>
+          <t>15072</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31138</t>
+          <t>30203</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44059</t>
+          <t>44898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73989</t>
+          <t>75224</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46142</t>
+          <t>46143</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73601</t>
+          <t>74909</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99741</t>
+          <t>97530</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140881</t>
+          <t>141335</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123838</t>
+          <t>127811</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166658</t>
+          <t>171027</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173444</t>
+          <t>172598</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216686</t>
+          <t>216246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314148</t>
+          <t>311063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>373091</t>
+          <t>371274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>229959</t>
+          <t>227424</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>278524</t>
+          <t>276986</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221661</t>
+          <t>221317</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>265532</t>
+          <t>266073</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>464870</t>
+          <t>462812</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>530569</t>
+          <t>526402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101404</t>
+          <t>100119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139660</t>
+          <t>140563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45462</t>
+          <t>46567</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75099</t>
+          <t>74795</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155253</t>
+          <t>154637</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205170</t>
+          <t>203944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>20793</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>30263</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80973</t>
+          <t>81801</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>117526</t>
+          <t>117327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117040</t>
+          <t>117335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>157380</t>
+          <t>159631</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211317</t>
+          <t>207740</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266012</t>
+          <t>263009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>215645</t>
+          <t>214923</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>266222</t>
+          <t>264099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>230825</t>
+          <t>231770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>279409</t>
+          <t>279822</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>456804</t>
+          <t>461585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>532679</t>
+          <t>529956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,03%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>222077</t>
+          <t>221799</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>274517</t>
+          <t>273169</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>190553</t>
+          <t>189158</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>236849</t>
+          <t>237446</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>423903</t>
+          <t>423977</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>496172</t>
+          <t>492616</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55479</t>
+          <t>55490</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86699</t>
+          <t>87132</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36135</t>
+          <t>37080</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63627</t>
+          <t>63852</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98028</t>
+          <t>98179</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139210</t>
+          <t>141605</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>15744</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21971</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>155297</t>
+          <t>158059</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>206860</t>
+          <t>206390</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>177344</t>
+          <t>175063</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>222968</t>
+          <t>225832</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>342032</t>
+          <t>343782</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>412582</t>
+          <t>415889</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195920</t>
+          <t>199562</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>250100</t>
+          <t>250381</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>213476</t>
+          <t>213774</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>261557</t>
+          <t>264132</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>427546</t>
+          <t>428346</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>499911</t>
+          <t>497784</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>167695</t>
+          <t>167786</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>215944</t>
+          <t>216128</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>152428</t>
+          <t>154045</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>198928</t>
+          <t>198707</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>335112</t>
+          <t>336345</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>401309</t>
+          <t>399901</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27509</t>
+          <t>28885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53026</t>
+          <t>54473</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>18364</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39270</t>
+          <t>38286</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51517</t>
+          <t>51413</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85239</t>
+          <t>83724</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19457</t>
+          <t>18660</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>27273</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>177926</t>
+          <t>176797</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>222751</t>
+          <t>223329</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>215744</t>
+          <t>218520</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>261469</t>
+          <t>263684</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>408165</t>
+          <t>408959</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>474500</t>
+          <t>473594</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,03%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>133348</t>
+          <t>135147</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>177211</t>
+          <t>176366</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>139641</t>
+          <t>139476</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>185344</t>
+          <t>183307</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>285905</t>
+          <t>283144</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>347368</t>
+          <t>345953</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>75431</t>
+          <t>74441</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>110805</t>
+          <t>110451</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>56828</t>
+          <t>56968</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>89771</t>
+          <t>90958</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>140103</t>
+          <t>142254</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>189331</t>
+          <t>190151</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34466</t>
+          <t>34385</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14188</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>34388</t>
+          <t>33893</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32977</t>
+          <t>33481</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>60868</t>
+          <t>59918</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>182553</t>
+          <t>182605</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>218836</t>
+          <t>218813</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>233459</t>
+          <t>234820</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>270062</t>
+          <t>271516</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>424720</t>
+          <t>426788</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>478778</t>
+          <t>476716</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,33%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>70452</t>
+          <t>69873</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>102947</t>
+          <t>103736</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>68706</t>
+          <t>66946</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>101462</t>
+          <t>100344</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>146096</t>
+          <t>149189</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>195063</t>
+          <t>193543</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>22860</t>
+          <t>22346</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>44804</t>
+          <t>43947</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>18722</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>39363</t>
+          <t>40848</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>48587</t>
+          <t>47910</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>77809</t>
+          <t>78465</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>33150</t>
+          <t>34097</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>169458</t>
+          <t>168981</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>195392</t>
+          <t>195032</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,82 +4838,82 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
+          <t>77,5%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>290016</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>269256</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>309474</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>74,73%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>69,38%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>79,74%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>472952</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>448336</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>496720</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>73,93%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>70,08%</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
           <t>77,64%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>290016</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>268479</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>308888</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>74,73%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>69,18%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>79,59%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>472952</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>447510</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>496366</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>73,93%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>69,95%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>77,59%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>38683</t>
+          <t>38356</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>62148</t>
+          <t>61252</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>45952</t>
+          <t>45959</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>80050</t>
+          <t>79609</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>91429</t>
+          <t>91282</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>132329</t>
+          <t>132970</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>18225</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>17789</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>41394</t>
+          <t>42151</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>26351</t>
+          <t>27713</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>54258</t>
+          <t>52796</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,47 +5212,47 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>17812</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>11100</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>29130</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
           <t>4,55%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>17812</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>10505</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>27406</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>897334</t>
+          <t>899003</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1001461</t>
+          <t>1004642</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1153062</t>
+          <t>1151031</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1276601</t>
+          <t>1270230</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2077914</t>
+          <t>2083449</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2243588</t>
+          <t>2238168</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>936667</t>
+          <t>935850</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1045827</t>
+          <t>1046921</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1023676</t>
+          <t>1029472</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1138553</t>
+          <t>1138552</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2002530</t>
+          <t>1998594</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2156320</t>
+          <t>2154891</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>961804</t>
+          <t>961148</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1067920</t>
+          <t>1071612</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>897494</t>
+          <t>899730</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1003386</t>
+          <t>1009133</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1888142</t>
+          <t>1885584</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2032748</t>
+          <t>2039403</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>338724</t>
+          <t>338570</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>412252</t>
+          <t>411121</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>222887</t>
+          <t>219845</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>280751</t>
+          <t>279759</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>580748</t>
+          <t>576099</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>672448</t>
+          <t>670743</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>34685</t>
+          <t>33937</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>61061</t>
+          <t>60979</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>17628</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>37412</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>55902</t>
+          <t>56560</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>89227</t>
+          <t>89736</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -6417,32 +6417,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27262</t>
+          <t>29249</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>16048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51149</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6452,32 +6452,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>29124</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37944</t>
+          <t>46017</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6487,32 +6487,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>48776</t>
+          <t>58373</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29380</t>
+          <t>38708</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71936</t>
+          <t>84990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -6530,32 +6530,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>129154</t>
+          <t>117961</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99250</t>
+          <t>89517</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166867</t>
+          <t>148617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6565,32 +6565,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>122960</t>
+          <t>139954</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101626</t>
+          <t>116853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144292</t>
+          <t>167767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6600,32 +6600,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>252114</t>
+          <t>257915</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>212816</t>
+          <t>217676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>296329</t>
+          <t>297896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -6643,32 +6643,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>192471</t>
+          <t>207207</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>158794</t>
+          <t>173657</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>226669</t>
+          <t>238351</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6678,32 +6678,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>133514</t>
+          <t>151146</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110881</t>
+          <t>125097</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>157319</t>
+          <t>176481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6713,32 +6713,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>325985</t>
+          <t>358353</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>284244</t>
+          <t>320311</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>369189</t>
+          <t>402591</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -6756,32 +6756,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47014</t>
+          <t>48920</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28820</t>
+          <t>30754</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75319</t>
+          <t>74122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6791,32 +6791,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31802</t>
+          <t>36492</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>23640</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48261</t>
+          <t>55060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6826,32 +6826,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>78817</t>
+          <t>85412</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54846</t>
+          <t>61432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107546</t>
+          <t>115218</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9978</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6939,32 +6939,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -6982,17 +6982,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7017,17 +7017,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7052,17 +7052,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7099,32 +7099,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33236</t>
+          <t>38882</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22005</t>
+          <t>25672</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48404</t>
+          <t>55997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7134,32 +7134,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>58436</t>
+          <t>74037</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>58777</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77146</t>
+          <t>93851</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7169,32 +7169,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>91672</t>
+          <t>112920</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68398</t>
+          <t>91381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116233</t>
+          <t>139923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -7212,32 +7212,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>170234</t>
+          <t>181424</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144954</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>193984</t>
+          <t>209771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7247,32 +7247,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>214538</t>
+          <t>235824</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116783</t>
+          <t>211694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255769</t>
+          <t>259109</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7282,32 +7282,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>384772</t>
+          <t>417248</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>290047</t>
+          <t>381120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>430100</t>
+          <t>452383</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -7325,32 +7325,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>187708</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137186</t>
+          <t>162105</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>184704</t>
+          <t>218148</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7360,32 +7360,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>221398</t>
+          <t>173699</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167002</t>
+          <t>151173</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347257</t>
+          <t>197496</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7395,32 +7395,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>381458</t>
+          <t>361408</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>324997</t>
+          <t>326197</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>528603</t>
+          <t>397155</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -7438,32 +7438,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52302</t>
+          <t>60434</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36204</t>
+          <t>43658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72350</t>
+          <t>83744</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7473,32 +7473,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28507</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7508,32 +7508,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>69433</t>
+          <t>77956</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48710</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93525</t>
+          <t>102452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -7551,32 +7551,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>19192</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7621,32 +7621,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -7664,17 +7664,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7699,17 +7699,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7734,17 +7734,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>80780</t>
+          <t>99729</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64795</t>
+          <t>80432</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98792</t>
+          <t>119011</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7816,32 +7816,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>108491</t>
+          <t>127394</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94258</t>
+          <t>110951</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123605</t>
+          <t>145399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7851,32 +7851,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>189271</t>
+          <t>227123</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167148</t>
+          <t>201307</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>213502</t>
+          <t>252798</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -7894,32 +7894,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>249071</t>
+          <t>292346</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>225088</t>
+          <t>264324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>273753</t>
+          <t>320499</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7929,32 +7929,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>257809</t>
+          <t>293240</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>240144</t>
+          <t>273104</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>277838</t>
+          <t>314967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7964,32 +7964,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>506881</t>
+          <t>585586</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>477521</t>
+          <t>552911</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>539032</t>
+          <t>618493</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -8007,32 +8007,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>165151</t>
+          <t>182355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>142689</t>
+          <t>158327</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>188425</t>
+          <t>209074</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8042,32 +8042,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>146347</t>
+          <t>166631</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>128726</t>
+          <t>148876</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162869</t>
+          <t>185051</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8077,32 +8077,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>311498</t>
+          <t>348986</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>285138</t>
+          <t>317910</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>342127</t>
+          <t>377964</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -8120,32 +8120,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31898</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>24723</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44008</t>
+          <t>49525</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8155,32 +8155,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24775</t>
+          <t>28880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18162</t>
+          <t>20453</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33772</t>
+          <t>38931</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8190,32 +8190,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>56673</t>
+          <t>64881</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>51498</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71579</t>
+          <t>81465</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -8233,32 +8233,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8268,32 +8268,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23464</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -8346,17 +8346,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8381,17 +8381,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>540814</t>
+          <t>620468</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>540814</t>
+          <t>620468</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>540814</t>
+          <t>620468</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8416,17 +8416,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1077153</t>
+          <t>1241305</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1077153</t>
+          <t>1241305</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1077153</t>
+          <t>1241305</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8463,32 +8463,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>134301</t>
+          <t>144228</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56967</t>
+          <t>124126</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195616</t>
+          <t>167324</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>174824</t>
+          <t>195247</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149995</t>
+          <t>176108</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197050</t>
+          <t>215413</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8533,32 +8533,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>309124</t>
+          <t>339475</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>182354</t>
+          <t>312107</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>377573</t>
+          <t>369690</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -8576,32 +8576,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>311526</t>
+          <t>332319</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>133939</t>
+          <t>303865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>441864</t>
+          <t>359666</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8611,32 +8611,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>307072</t>
+          <t>330393</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>261184</t>
+          <t>307840</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>331029</t>
+          <t>352531</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8646,32 +8646,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>618598</t>
+          <t>662712</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>367740</t>
+          <t>628915</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>746872</t>
+          <t>696744</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>48,66%</t>
         </is>
       </c>
     </row>
@@ -8689,32 +8689,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>155263</t>
+          <t>173237</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>71387</t>
+          <t>149455</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>225581</t>
+          <t>198841</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8724,32 +8724,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>202300</t>
+          <t>180047</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>171033</t>
+          <t>161179</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>287583</t>
+          <t>198558</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8759,32 +8759,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>357563</t>
+          <t>353284</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>225415</t>
+          <t>323808</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>452201</t>
+          <t>385383</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -8802,32 +8802,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>33783</t>
+          <t>41110</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12668</t>
+          <t>29248</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53314</t>
+          <t>56639</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8837,32 +8837,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>25380</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>18030</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31119</t>
+          <t>34261</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8872,32 +8872,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>56687</t>
+          <t>66490</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>53784</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73677</t>
+          <t>83060</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -8915,32 +8915,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>251037</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>619575</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8950,32 +8950,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8985,32 +8985,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>253041</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>758297</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -9028,17 +9028,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>885909</t>
+          <t>698817</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>885909</t>
+          <t>698817</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>885909</t>
+          <t>698817</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9063,17 +9063,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>709104</t>
+          <t>733074</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>709104</t>
+          <t>733074</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>709104</t>
+          <t>733074</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9098,17 +9098,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1595013</t>
+          <t>1431891</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1595013</t>
+          <t>1431891</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1595013</t>
+          <t>1431891</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9145,32 +9145,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>186627</t>
+          <t>200255</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>166895</t>
+          <t>179262</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>208337</t>
+          <t>222344</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9180,32 +9180,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>245741</t>
+          <t>270703</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>228886</t>
+          <t>251818</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>261671</t>
+          <t>289753</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9215,32 +9215,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>432368</t>
+          <t>470958</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>407103</t>
+          <t>440821</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>460332</t>
+          <t>502135</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -9258,32 +9258,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>230662</t>
+          <t>251757</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>210868</t>
+          <t>228505</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>252827</t>
+          <t>275594</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9293,32 +9293,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>213819</t>
+          <t>239249</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>196306</t>
+          <t>219770</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>229802</t>
+          <t>257144</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9328,32 +9328,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>444481</t>
+          <t>491007</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>416947</t>
+          <t>461251</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>471409</t>
+          <t>521034</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,9%</t>
         </is>
       </c>
     </row>
@@ -9371,32 +9371,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>119201</t>
+          <t>128160</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>101102</t>
+          <t>109547</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>137555</t>
+          <t>146854</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9406,32 +9406,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>77516</t>
+          <t>87220</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66026</t>
+          <t>74074</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>90900</t>
+          <t>102027</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9441,32 +9441,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>196717</t>
+          <t>215380</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>175626</t>
+          <t>194224</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>219388</t>
+          <t>240239</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -9484,32 +9484,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>18541</t>
+          <t>22951</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>14684</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>34523</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9519,32 +9519,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7832</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9554,32 +9554,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>25658</t>
+          <t>30783</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>36264</t>
+          <t>43709</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -9597,69 +9597,69 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9705</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>1692</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>4567</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -9667,32 +9667,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11285</t>
+          <t>12044</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -9710,17 +9710,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>559513</t>
+          <t>607624</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>559513</t>
+          <t>607624</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>559513</t>
+          <t>607624</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9745,17 +9745,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>545885</t>
+          <t>606822</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>545885</t>
+          <t>606822</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>545885</t>
+          <t>606822</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9780,17 +9780,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1105398</t>
+          <t>1214447</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1105398</t>
+          <t>1214447</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1105398</t>
+          <t>1214447</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9827,32 +9827,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>186773</t>
+          <t>204731</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>171863</t>
+          <t>186686</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>202686</t>
+          <t>219661</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9862,32 +9862,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>444908</t>
+          <t>258476</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>352944</t>
+          <t>244184</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>533040</t>
+          <t>274626</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9897,32 +9897,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>631681</t>
+          <t>463207</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>530896</t>
+          <t>439204</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>793315</t>
+          <t>485670</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -9940,32 +9940,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>120303</t>
+          <t>134389</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>106596</t>
+          <t>119572</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>133727</t>
+          <t>150117</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9975,32 +9975,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>115475</t>
+          <t>126843</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>113160</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>181510</t>
+          <t>140777</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10010,32 +10010,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>235778</t>
+          <t>261233</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>120807</t>
+          <t>242153</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>305146</t>
+          <t>284050</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -10053,32 +10053,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>48681</t>
+          <t>54411</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>44287</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>58792</t>
+          <t>67114</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>42449</t>
+          <t>47346</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>18012</t>
+          <t>37585</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>68801</t>
+          <t>57367</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>91130</t>
+          <t>101756</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>46863</t>
+          <t>87285</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>119649</t>
+          <t>116847</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -10166,32 +10166,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>11775</t>
+          <t>12880</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10201,32 +10201,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>12483</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>26215</t>
+          <t>27201</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>669</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>666</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -10339,34 +10339,34 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>4018</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>3419</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -10392,17 +10392,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10427,17 +10427,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10509,32 +10509,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>185825</t>
+          <t>202975</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>173173</t>
+          <t>189358</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>199298</t>
+          <t>216676</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10544,32 +10544,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>301431</t>
+          <t>328187</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>289291</t>
+          <t>313140</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>315264</t>
+          <t>343429</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10579,32 +10579,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>487256</t>
+          <t>531162</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>467923</t>
+          <t>509278</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>505048</t>
+          <t>550479</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
@@ -10622,32 +10622,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>63020</t>
+          <t>69497</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>56872</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>75052</t>
+          <t>81904</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10657,32 +10657,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>86757</t>
+          <t>94675</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>74585</t>
+          <t>81940</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>98175</t>
+          <t>107517</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10692,32 +10692,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>149777</t>
+          <t>164172</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>132796</t>
+          <t>148518</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>166178</t>
+          <t>183183</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -10735,32 +10735,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>28809</t>
+          <t>32081</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>21638</t>
+          <t>23860</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>41779</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10770,22 +10770,22 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>28916</t>
+          <t>31748</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>24170</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>36890</t>
+          <t>39910</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10805,32 +10805,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>57725</t>
+          <t>63829</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>47201</t>
+          <t>51811</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>68739</t>
+          <t>75514</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -10848,32 +10848,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10883,32 +10883,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>13796</t>
+          <t>16023</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10918,32 +10918,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -11074,17 +11074,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>282211</t>
+          <t>309639</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>282211</t>
+          <t>309639</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>282211</t>
+          <t>309639</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -11109,17 +11109,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>425241</t>
+          <t>463931</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>425241</t>
+          <t>463931</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>425241</t>
+          <t>463931</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -11144,17 +11144,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>707452</t>
+          <t>773569</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>707452</t>
+          <t>773569</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>707452</t>
+          <t>773569</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -11191,32 +11191,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>834803</t>
+          <t>920049</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>614773</t>
+          <t>863882</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>917807</t>
+          <t>980071</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11226,32 +11226,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1355346</t>
+          <t>1283169</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1189617</t>
+          <t>1236670</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1757464</t>
+          <t>1332745</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11261,32 +11261,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>2190148</t>
+          <t>2203219</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1961109</t>
+          <t>2124183</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2712969</t>
+          <t>2269486</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -11304,32 +11304,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1273970</t>
+          <t>1379694</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>933861</t>
+          <t>1318938</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1389789</t>
+          <t>1448922</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11339,32 +11339,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1318430</t>
+          <t>1460178</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1073259</t>
+          <t>1406293</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1431180</t>
+          <t>1512560</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11374,32 +11374,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2592400</t>
+          <t>2839873</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2244608</t>
+          <t>2754922</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2778971</t>
+          <t>2918886</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -11417,32 +11417,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>869637</t>
+          <t>965159</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>686162</t>
+          <t>899851</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>956248</t>
+          <t>1028300</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11452,32 +11452,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>852439</t>
+          <t>837836</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>719237</t>
+          <t>794643</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1025998</t>
+          <t>890390</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11487,32 +11487,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1722076</t>
+          <t>1802995</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1511104</t>
+          <t>1729827</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1922434</t>
+          <t>1880143</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -11530,32 +11530,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>199870</t>
+          <t>227382</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>154996</t>
+          <t>193132</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>237981</t>
+          <t>267863</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11565,32 +11565,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>117243</t>
+          <t>131262</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>92219</t>
+          <t>109331</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>141364</t>
+          <t>156911</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11600,32 +11600,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>317113</t>
+          <t>358644</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>266273</t>
+          <t>314570</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>367453</t>
+          <t>405004</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -11643,32 +11643,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>277391</t>
+          <t>36395</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>31995</t>
+          <t>25454</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1070221</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11678,32 +11678,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11713,32 +11713,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>286466</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>36958</t>
+          <t>35386</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1124660</t>
+          <t>68136</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -11756,17 +11756,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -11791,17 +11791,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -11826,17 +11826,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
